--- a/assets/constructions/examples/ctd_mie_90.xlsx
+++ b/assets/constructions/examples/ctd_mie_90.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,56 +584,74 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AHU-C16-16-180-2T</t>
+          <t>021E20090-05-04-020090</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AHU</t>
+          <t>20090</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.6</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>JDMT100308</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -641,10 +659,10 @@
         <v>90</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -656,184 +674,202 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>HA-16</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DER_JD1003H</t>
+          <t>PALB_XP0602H</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>15.8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>JD1003_H</t>
+          <t>PALB_XP0602_H</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
+          <t>2020 / PALBIT основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>334.72</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>30772.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT190-032Z32R04BD10-L160-IK</t>
+          <t>TP-C32-40-200-3T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MT190-Z...BD10-IK</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>34800</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0.6</v>
+        <v>1.21</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BD.T10T3.ER</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>TPMN160308</t>
+        </is>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
         <v>90</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HA-32</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>ISO_TP1603W</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>HA</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>HA-32</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>SKIF_BD10T3H</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>SKIF_BD10T3H</t>
+          <t>TP1603W</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TP-C25-35-200-2T</t>
+          <t>VSM11D032Z04B25XD11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>VSM11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
         <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="H4" t="n">
         <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25800</v>
+      </c>
       <c r="M4" t="n">
-        <v>0.8</v>
+        <v>0.35</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>11.4</v>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>TPMN160308</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -841,14 +877,14 @@
         <v>90</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -856,187 +892,193 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>ISO_TP1603W</t>
+          <t>WIDIA_XD1104H</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>TP1603W</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+          <t>WID_XD1104_H</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>WID_VSM11D_1669</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2019 / Novo</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSM490D032Z04A32XN15L200</t>
+          <t>STGF90A-D22-20-45-120-2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VSM490-15</t>
+          <t>STGF90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>22000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.14</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TPKN1103</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>90</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HB-20</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>ISO_TP1103W</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
         <v>3</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>HA</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>HA-32</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>WIDIA_XN15T6H</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>WID_XN15T6_H</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>WID_VSM490_2133</t>
-        </is>
-      </c>
+          <t>TP1103W</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2018 / WIDIA достижения</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300R-C15-16-200-2T</t>
+          <t>R200-D30-25-40-120-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>300R</t>
+          <t>R200</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H6" t="n">
         <v>40</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>0.26</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>APMT1135</t>
-        </is>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
+          <t>APKT1003</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>90</v>
       </c>
@@ -1056,33 +1098,39 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>HA-15</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>DER_AP1135H</t>
+          <t>LIKON_AP1003H</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>AP1135_H</t>
+          <t>LIK_AP1003H</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
